--- a/Docs/오락실(5팀)_기능명세_일정관리표_v0.5.xlsx
+++ b/Docs/오락실(5팀)_기능명세_일정관리표_v0.5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Space13ound\01. Study\UnityTeamProject\Git\BillsMustBePaid\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE9BBA2-87A9-4BB2-9916-667F49D4749B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F2CD2C-9AB8-4E0D-AC38-05008B03B6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3840" yWindow="3840" windowWidth="23040" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="오락실(5팀) 기능명세 &amp; 일정관리표" sheetId="1" r:id="rId1"/>
@@ -1947,13 +1947,13 @@
   </cellStyles>
   <dxfs count="6">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
@@ -1993,10 +1993,10 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="우선순위"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="레벨" dataDxfId="4"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="난이도" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="담당자" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="담당자" dataDxfId="2"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="상세설명"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="예상 공수 (H)" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="완료예정일 (yyyy-MM-dd)" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="예상 공수 (H)" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="완료예정일 (yyyy-MM-dd)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/Docs/오락실(5팀)_기능명세_일정관리표_v0.5.xlsx
+++ b/Docs/오락실(5팀)_기능명세_일정관리표_v0.5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Space13ound\01. Study\UnityTeamProject\Git\BillsMustBePaid\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F2CD2C-9AB8-4E0D-AC38-05008B03B6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F406AD01-DC97-49DC-96BE-A30BBE0C0320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="3840" windowWidth="23040" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="오락실(5팀) 기능명세 &amp; 일정관리표" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="604">
   <si>
     <t>이펙트 및 사운드 중복 재생 방지</t>
   </si>
@@ -1796,6 +1796,54 @@
   <si>
     <t>김민재</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-10-20</t>
+  </si>
+  <si>
+    <t>2026-10-22</t>
+  </si>
+  <si>
+    <t>2026-10-23</t>
+  </si>
+  <si>
+    <t>2026-10-27</t>
+  </si>
+  <si>
+    <t>2026-11-03</t>
+  </si>
+  <si>
+    <t>2026-10-28</t>
+  </si>
+  <si>
+    <t>2026-10-29</t>
+  </si>
+  <si>
+    <t>2026-11-05</t>
+  </si>
+  <si>
+    <t>2026-11-06</t>
+  </si>
+  <si>
+    <t>2026-10-30</t>
+  </si>
+  <si>
+    <t>2026-11-04</t>
+  </si>
+  <si>
+    <t>2026-11-10</t>
+  </si>
+  <si>
+    <t>2026-11-12</t>
+  </si>
+  <si>
+    <t>2026-11-13</t>
+  </si>
+  <si>
+    <t>2026-11-09</t>
+  </si>
+  <si>
+    <t>2026-11-11</t>
   </si>
 </sst>
 </file>
@@ -2470,8 +2518,8 @@
       <c r="K9" s="7">
         <v>2</v>
       </c>
-      <c r="L9" s="8">
-        <v>46315</v>
+      <c r="L9" s="8" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="10" spans="2:12">
@@ -2505,8 +2553,8 @@
       <c r="K10" s="7">
         <v>2</v>
       </c>
-      <c r="L10" s="8">
-        <v>46315</v>
+      <c r="L10" s="8" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="11" spans="2:12">
@@ -2540,8 +2588,8 @@
       <c r="K11" s="7">
         <v>1</v>
       </c>
-      <c r="L11" s="8">
-        <v>46315</v>
+      <c r="L11" s="8" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="12" spans="2:12">
@@ -2575,8 +2623,8 @@
       <c r="K12" s="7">
         <v>1</v>
       </c>
-      <c r="L12" s="8">
-        <v>46315</v>
+      <c r="L12" s="8" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="13" spans="2:12">
@@ -2610,8 +2658,8 @@
       <c r="K13" s="7">
         <v>1</v>
       </c>
-      <c r="L13" s="8">
-        <v>46315</v>
+      <c r="L13" s="8" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="14" spans="2:12">
@@ -2645,8 +2693,8 @@
       <c r="K14" s="7">
         <v>1</v>
       </c>
-      <c r="L14" s="8">
-        <v>46315</v>
+      <c r="L14" s="8" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="15" spans="2:12">
@@ -2680,8 +2728,8 @@
       <c r="K15" s="7">
         <v>1</v>
       </c>
-      <c r="L15" s="8">
-        <v>46315</v>
+      <c r="L15" s="8" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -2715,8 +2763,8 @@
       <c r="K16" s="7">
         <v>2</v>
       </c>
-      <c r="L16" s="8">
-        <v>46315</v>
+      <c r="L16" s="8" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -2750,8 +2798,8 @@
       <c r="K17" s="7">
         <v>4</v>
       </c>
-      <c r="L17" s="8">
-        <v>46315</v>
+      <c r="L17" s="8" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="18" spans="2:12">
@@ -2785,8 +2833,8 @@
       <c r="K18" s="7">
         <v>3</v>
       </c>
-      <c r="L18" s="8">
-        <v>46315</v>
+      <c r="L18" s="8" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="19" spans="2:12">
@@ -2820,8 +2868,8 @@
       <c r="K19" s="7">
         <v>2</v>
       </c>
-      <c r="L19" s="8">
-        <v>46315</v>
+      <c r="L19" s="8" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -2855,8 +2903,8 @@
       <c r="K20" s="7">
         <v>2</v>
       </c>
-      <c r="L20" s="8">
-        <v>46315</v>
+      <c r="L20" s="8" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="21" spans="2:12">
@@ -2890,8 +2938,8 @@
       <c r="K21" s="7">
         <v>2</v>
       </c>
-      <c r="L21" s="8">
-        <v>46315</v>
+      <c r="L21" s="8" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="22" spans="2:12">
@@ -2925,8 +2973,8 @@
       <c r="K22" s="7">
         <v>4</v>
       </c>
-      <c r="L22" s="8">
-        <v>46315</v>
+      <c r="L22" s="8" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="23" spans="2:12">
@@ -2960,8 +3008,8 @@
       <c r="K23" s="7">
         <v>3</v>
       </c>
-      <c r="L23" s="8">
-        <v>46315</v>
+      <c r="L23" s="8" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="24" spans="2:12">
@@ -2995,8 +3043,8 @@
       <c r="K24" s="7">
         <v>4</v>
       </c>
-      <c r="L24" s="8">
-        <v>46315</v>
+      <c r="L24" s="8" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="25" spans="2:12">
@@ -3030,8 +3078,8 @@
       <c r="K25" s="7">
         <v>4</v>
       </c>
-      <c r="L25" s="8">
-        <v>46315</v>
+      <c r="L25" s="8" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -3065,8 +3113,8 @@
       <c r="K26" s="7">
         <v>3</v>
       </c>
-      <c r="L26" s="8">
-        <v>46315</v>
+      <c r="L26" s="8" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -3100,8 +3148,8 @@
       <c r="K27" s="7">
         <v>3</v>
       </c>
-      <c r="L27" s="8">
-        <v>46315</v>
+      <c r="L27" s="8" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="28" spans="2:12">
@@ -3135,8 +3183,8 @@
       <c r="K28" s="7">
         <v>3</v>
       </c>
-      <c r="L28" s="8">
-        <v>46315</v>
+      <c r="L28" s="8" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="29" spans="2:12">
@@ -3170,8 +3218,8 @@
       <c r="K29" s="7">
         <v>2</v>
       </c>
-      <c r="L29" s="8">
-        <v>46315</v>
+      <c r="L29" s="8" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="30" spans="2:12">
@@ -3205,8 +3253,8 @@
       <c r="K30" s="7">
         <v>5</v>
       </c>
-      <c r="L30" s="8">
-        <v>46315</v>
+      <c r="L30" s="8" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="31" spans="2:12">
@@ -3240,8 +3288,8 @@
       <c r="K31" s="7">
         <v>5</v>
       </c>
-      <c r="L31" s="8">
-        <v>46315</v>
+      <c r="L31" s="8" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="32" spans="2:12">
@@ -3275,8 +3323,8 @@
       <c r="K32" s="7">
         <v>4</v>
       </c>
-      <c r="L32" s="8">
-        <v>46315</v>
+      <c r="L32" s="8" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="33" spans="2:12">
@@ -3310,8 +3358,8 @@
       <c r="K33" s="7">
         <v>4</v>
       </c>
-      <c r="L33" s="8">
-        <v>46315</v>
+      <c r="L33" s="8" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -3345,8 +3393,8 @@
       <c r="K34" s="7">
         <v>4</v>
       </c>
-      <c r="L34" s="8">
-        <v>46315</v>
+      <c r="L34" s="8" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="35" spans="2:12">
@@ -3380,8 +3428,8 @@
       <c r="K35" s="7">
         <v>4</v>
       </c>
-      <c r="L35" s="8">
-        <v>46315</v>
+      <c r="L35" s="8" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="36" spans="2:12">
@@ -3415,8 +3463,8 @@
       <c r="K36" s="7">
         <v>4</v>
       </c>
-      <c r="L36" s="8">
-        <v>46315</v>
+      <c r="L36" s="8" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="37" spans="2:12">
@@ -3450,8 +3498,8 @@
       <c r="K37" s="7">
         <v>3</v>
       </c>
-      <c r="L37" s="8">
-        <v>46315</v>
+      <c r="L37" s="8" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="38" spans="2:12">
@@ -3485,8 +3533,8 @@
       <c r="K38" s="7">
         <v>3</v>
       </c>
-      <c r="L38" s="8">
-        <v>46315</v>
+      <c r="L38" s="8" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -3520,8 +3568,8 @@
       <c r="K39" s="7">
         <v>3</v>
       </c>
-      <c r="L39" s="8">
-        <v>46315</v>
+      <c r="L39" s="8" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="40" spans="2:12">
@@ -3555,8 +3603,8 @@
       <c r="K40" s="7">
         <v>3</v>
       </c>
-      <c r="L40" s="8">
-        <v>46315</v>
+      <c r="L40" s="8" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="41" spans="2:12">
@@ -3590,8 +3638,8 @@
       <c r="K41" s="7">
         <v>8</v>
       </c>
-      <c r="L41" s="8">
-        <v>46315</v>
+      <c r="L41" s="8" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="42" spans="2:12">
@@ -3625,8 +3673,8 @@
       <c r="K42" s="7">
         <v>8</v>
       </c>
-      <c r="L42" s="8">
-        <v>46315</v>
+      <c r="L42" s="8" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="43" spans="2:12">
@@ -3660,8 +3708,8 @@
       <c r="K43" s="7">
         <v>5</v>
       </c>
-      <c r="L43" s="8">
-        <v>46315</v>
+      <c r="L43" s="8" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="44" spans="2:12">
@@ -3695,8 +3743,8 @@
       <c r="K44" s="7">
         <v>3</v>
       </c>
-      <c r="L44" s="8">
-        <v>46315</v>
+      <c r="L44" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="45" spans="2:12">
@@ -3730,8 +3778,8 @@
       <c r="K45" s="7">
         <v>3</v>
       </c>
-      <c r="L45" s="8">
-        <v>46315</v>
+      <c r="L45" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="46" spans="2:12">
@@ -3765,8 +3813,8 @@
       <c r="K46" s="7">
         <v>3</v>
       </c>
-      <c r="L46" s="8">
-        <v>46315</v>
+      <c r="L46" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="47" spans="2:12">
@@ -3800,8 +3848,8 @@
       <c r="K47" s="7">
         <v>8</v>
       </c>
-      <c r="L47" s="8">
-        <v>46315</v>
+      <c r="L47" s="8" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="48" spans="2:12">
@@ -3835,8 +3883,8 @@
       <c r="K48" s="7">
         <v>5</v>
       </c>
-      <c r="L48" s="8">
-        <v>46315</v>
+      <c r="L48" s="8" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="49" spans="2:12">
@@ -3870,8 +3918,8 @@
       <c r="K49" s="7">
         <v>4</v>
       </c>
-      <c r="L49" s="8">
-        <v>46315</v>
+      <c r="L49" s="8" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="50" spans="2:12">
@@ -3905,8 +3953,8 @@
       <c r="K50" s="7">
         <v>4</v>
       </c>
-      <c r="L50" s="8">
-        <v>46315</v>
+      <c r="L50" s="8" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="51" spans="2:12" ht="52.2">
@@ -3940,8 +3988,8 @@
       <c r="K51" s="7">
         <v>3</v>
       </c>
-      <c r="L51" s="8">
-        <v>46315</v>
+      <c r="L51" s="8" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="52" spans="2:12" ht="34.799999999999997">
@@ -3975,8 +4023,8 @@
       <c r="K52" s="7">
         <v>3</v>
       </c>
-      <c r="L52" s="8">
-        <v>46315</v>
+      <c r="L52" s="8" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="53" spans="2:12">
@@ -4010,8 +4058,8 @@
       <c r="K53" s="7">
         <v>5</v>
       </c>
-      <c r="L53" s="8">
-        <v>46315</v>
+      <c r="L53" s="8" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="54" spans="2:12">
@@ -4045,8 +4093,8 @@
       <c r="K54" s="7">
         <v>3</v>
       </c>
-      <c r="L54" s="8">
-        <v>46315</v>
+      <c r="L54" s="8" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="55" spans="2:12">
@@ -4080,8 +4128,8 @@
       <c r="K55" s="7">
         <v>10</v>
       </c>
-      <c r="L55" s="8">
-        <v>46315</v>
+      <c r="L55" s="8" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="56" spans="2:12">
